--- a/Excel p1.xlsx
+++ b/Excel p1.xlsx
@@ -1,16 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\excel projct\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rahul\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3D1FDD80-66D3-494D-8126-5DED013978E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F7A28F5-0F9D-47B2-A936-3D1CC4AE2A1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="+ZZMylGf3s25ptfXyhwW3QnzoxtoC+EednXZk5+Jlb4lz2JY96k+cpACMws0wuXD9RmVVedIYFvlQvajFNdPMA==" workbookSaltValue="epn2SOsgt7lxGSnR6b1bQQ==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13875" firstSheet="2" activeTab="2" xr2:uid="{AD824907-F620-455A-BE5D-BE13FDB86898}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13875" xr2:uid="{AD824907-F620-455A-BE5D-BE13FDB86898}"/>
   </bookViews>
   <sheets>
     <sheet name="Sales Data" sheetId="2" r:id="rId1"/>
@@ -43,7 +44,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -65,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="174">
   <si>
     <t>Student id</t>
   </si>
@@ -508,9 +509,6 @@
     <t>DYNAMIC CELL REFERANCE</t>
   </si>
   <si>
-    <t>B3</t>
-  </si>
-  <si>
     <t>DYANAMIC OUTPUT</t>
   </si>
   <si>
@@ -584,6 +582,12 @@
   </si>
   <si>
     <t>TOP STUDENT</t>
+  </si>
+  <si>
+    <t>YES</t>
+  </si>
+  <si>
+    <t>B4</t>
   </si>
 </sst>
 </file>
@@ -591,7 +595,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="169" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
+    <numFmt numFmtId="164" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
   </numFmts>
   <fonts count="39">
     <font>
@@ -907,7 +911,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="14">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -1028,26 +1032,6 @@
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
         <color theme="5" tint="-0.249977111117893"/>
       </left>
       <right style="thin">
@@ -1080,7 +1064,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="69">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1163,7 +1147,7 @@
     <xf numFmtId="49" fontId="12" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="14" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -1186,15 +1170,6 @@
     <xf numFmtId="0" fontId="26" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1203,41 +1178,44 @@
     </xf>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="32" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="32" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1245,117 +1223,6 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="17">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="Imprint MT Shadow"/>
-        <family val="5"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="16"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="16"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="16"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="16"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -1450,6 +1317,45 @@
         <scheme val="none"/>
       </font>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Imprint MT Shadow"/>
+        <family val="5"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
@@ -1702,6 +1608,78 @@
         <bottom/>
       </border>
     </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -1716,11 +1694,11 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{1723CA0A-C5E6-44B3-9BAB-4C063923A42C}" name="Table2" displayName="Table2" ref="H8:I10" totalsRowShown="0" headerRowDxfId="1" dataDxfId="2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{1723CA0A-C5E6-44B3-9BAB-4C063923A42C}" name="Table2" displayName="Table2" ref="H8:I10" totalsRowShown="0" headerRowDxfId="16" dataDxfId="15">
   <autoFilter ref="H8:I10" xr:uid="{1723CA0A-C5E6-44B3-9BAB-4C063923A42C}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{FA1811F2-D3D9-4AEF-9FC0-BAB661DA9BC8}" name="Column1" dataDxfId="4"/>
-    <tableColumn id="2" xr3:uid="{E856F641-AAD9-4F61-B9C0-4DCD5635EC84}" name="Column2" dataDxfId="3">
+    <tableColumn id="1" xr3:uid="{FA1811F2-D3D9-4AEF-9FC0-BAB661DA9BC8}" name="Column1" dataDxfId="14"/>
+    <tableColumn id="2" xr3:uid="{E856F641-AAD9-4F61-B9C0-4DCD5635EC84}" name="Column2" dataDxfId="13">
       <calculatedColumnFormula>VLOOKUP(I8,A1:E20,3,FALSE)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -1729,23 +1707,23 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1BA5C808-9BFC-446D-903C-4CC0175240D9}" name="Table1" displayName="Table1" ref="A1:H21" totalsRowShown="0" headerRowDxfId="16" dataDxfId="14" headerRowBorderDxfId="15" tableBorderDxfId="13" totalsRowBorderDxfId="12">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1BA5C808-9BFC-446D-903C-4CC0175240D9}" name="Table1" displayName="Table1" ref="A1:H21" totalsRowShown="0" headerRowDxfId="12" dataDxfId="10" headerRowBorderDxfId="11" tableBorderDxfId="9" totalsRowBorderDxfId="8">
   <autoFilter ref="A1:H21" xr:uid="{1BA5C808-9BFC-446D-903C-4CC0175240D9}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{C737360A-3427-4AA1-ACAB-E6EAD43BA20E}" name="Student id" dataDxfId="11"/>
-    <tableColumn id="2" xr3:uid="{34200D63-52BF-4C24-8CA9-FD902EABCB02}" name="Student name" dataDxfId="10"/>
-    <tableColumn id="3" xr3:uid="{58E9C5AD-BC48-4710-ADD1-9AD8E241941A}" name="Maths" dataDxfId="9"/>
-    <tableColumn id="4" xr3:uid="{A15FF5E2-348C-46F0-9B38-CA331205CC96}" name="Science" dataDxfId="8"/>
-    <tableColumn id="5" xr3:uid="{F0FE34EC-CB0E-41BC-B23F-9621F70060FC}" name="Score" dataDxfId="0">
+    <tableColumn id="1" xr3:uid="{C737360A-3427-4AA1-ACAB-E6EAD43BA20E}" name="Student id" dataDxfId="7"/>
+    <tableColumn id="2" xr3:uid="{34200D63-52BF-4C24-8CA9-FD902EABCB02}" name="Student name" dataDxfId="6"/>
+    <tableColumn id="3" xr3:uid="{58E9C5AD-BC48-4710-ADD1-9AD8E241941A}" name="Maths" dataDxfId="5"/>
+    <tableColumn id="4" xr3:uid="{A15FF5E2-348C-46F0-9B38-CA331205CC96}" name="Science" dataDxfId="4"/>
+    <tableColumn id="5" xr3:uid="{F0FE34EC-CB0E-41BC-B23F-9621F70060FC}" name="Score" dataDxfId="3">
       <calculatedColumnFormula>AVERAGE(C2:D2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{8A596D2F-3F86-4074-A4EF-4E9FA8A802C0}" name="Grade" dataDxfId="7">
+    <tableColumn id="6" xr3:uid="{8A596D2F-3F86-4074-A4EF-4E9FA8A802C0}" name="Grade" dataDxfId="2">
       <calculatedColumnFormula>IF(E2&gt;=90,"A",IF(E2&gt;=80,"B",IF(E2&gt;=70,"C",IF(E2&gt;=60,"D",IF(E2&gt;=50,"E",IF(E2&gt;=40,"F","Fail"))))))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{D2182CFE-B181-45C4-B61A-FB679D3BC0C7}" name="Above 80?" dataDxfId="6">
+    <tableColumn id="7" xr3:uid="{D2182CFE-B181-45C4-B61A-FB679D3BC0C7}" name="Above 80?" dataDxfId="1">
       <calculatedColumnFormula>IF(E2&gt;80,"Yes","No")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{696DD799-F794-4861-A8CC-AA51E529D66E}" name="Math &amp; Science Above 80?" dataDxfId="5">
+    <tableColumn id="8" xr3:uid="{696DD799-F794-4861-A8CC-AA51E529D66E}" name="Math &amp; Science Above 80?" dataDxfId="0">
       <calculatedColumnFormula>IF(AND(C2&gt;80,D2&gt;80),"OK","NOT OK")</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -2132,7 +2110,6 @@
         <v>NO</v>
       </c>
       <c r="H3" s="42">
-        <f>SUMIFS($C$2:$C$21,$B$2:$B$21,B2)</f>
         <v>300</v>
       </c>
     </row>
@@ -2154,9 +2131,8 @@
         <f t="shared" si="1"/>
         <v>2500</v>
       </c>
-      <c r="F4" s="32" t="str">
-        <f t="shared" si="2"/>
-        <v>NO</v>
+      <c r="F4" s="32" t="s">
+        <v>172</v>
       </c>
       <c r="O4" t="s">
         <v>58</v>
@@ -2226,9 +2202,8 @@
         <f t="shared" si="1"/>
         <v>7200</v>
       </c>
-      <c r="F7" s="32" t="str">
-        <f t="shared" si="2"/>
-        <v>YES</v>
+      <c r="F7" s="32" t="s">
+        <v>172</v>
       </c>
     </row>
     <row r="8" spans="1:15" ht="22.15">
@@ -2746,6 +2721,7 @@
       <c r="F41" s="15"/>
     </row>
   </sheetData>
+  <sheetProtection algorithmName="SHA-512" hashValue="uYRdOyHd2ysIUz081TnkIqT3hUmGtTQhHbqcVxOWq3iblRofiWdL46exKB2uLP2DO080VkiGYvDhkBUvDRD8tA==" saltValue="tXa/4x02mKNxVKidQmzEWQ==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
@@ -3865,6 +3841,7 @@
       <c r="O41" s="34"/>
     </row>
   </sheetData>
+  <sheetProtection algorithmName="SHA-512" hashValue="SteDfQ9jwNo4BK1dkMoWKBhKfzzE2ttgTRPa1V7PekGj1Ca3tpqLf36XF9+zpVrn/Rk553KAVUIWUVO3LckA0w==" saltValue="c34PvJIRhsMnPSUnWJEKxA==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
@@ -3997,6 +3974,7 @@
       </c>
     </row>
   </sheetData>
+  <sheetProtection algorithmName="SHA-512" hashValue="zU12pLZQNnNi7kdPuCyjWXWshnIKlZMQ65ZteL6VL7Ob3LXpzsiVUnNwYe9tfJ1JMpCjR80goBIWH3RyGB48Og==" saltValue="HmzZQsoGBj+4BvJ4QYrBsg==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -4027,13 +4005,13 @@
       <c r="D1" s="48" t="s">
         <v>132</v>
       </c>
-      <c r="E1" s="49" t="s">
+      <c r="E1" s="48" t="s">
         <v>140</v>
       </c>
-      <c r="F1" s="49" t="s">
+      <c r="F1" s="48" t="s">
         <v>139</v>
       </c>
-      <c r="G1" s="49" t="s">
+      <c r="G1" s="48" t="s">
         <v>141</v>
       </c>
     </row>
@@ -4050,13 +4028,13 @@
       <c r="D2" s="48" t="s">
         <v>137</v>
       </c>
-      <c r="E2" s="50">
+      <c r="E2" s="66">
         <v>50000</v>
       </c>
-      <c r="F2" s="51">
+      <c r="F2" s="48">
         <v>50000</v>
       </c>
-      <c r="G2" s="50">
+      <c r="G2" s="66">
         <f>_xlfn.XMATCH(F2, C:C, 0)</f>
         <v>2</v>
       </c>
@@ -4074,13 +4052,13 @@
       <c r="D3" s="48" t="s">
         <v>138</v>
       </c>
-      <c r="E3" s="50">
+      <c r="E3" s="66">
         <v>45000</v>
       </c>
-      <c r="F3" s="51">
+      <c r="F3" s="48">
         <v>76000</v>
       </c>
-      <c r="G3" s="50">
+      <c r="G3" s="66">
         <f t="shared" ref="G3:G6" si="0">_xlfn.XMATCH(F3, C:C, 0)</f>
         <v>5</v>
       </c>
@@ -4098,13 +4076,13 @@
       <c r="D4" s="48" t="s">
         <v>137</v>
       </c>
-      <c r="E4" s="50">
+      <c r="E4" s="66">
         <v>78000</v>
       </c>
-      <c r="F4" s="51">
+      <c r="F4" s="48">
         <v>78000</v>
       </c>
-      <c r="G4" s="50">
+      <c r="G4" s="66">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
@@ -4122,13 +4100,13 @@
       <c r="D5" s="48" t="s">
         <v>137</v>
       </c>
-      <c r="E5" s="50">
+      <c r="E5" s="66">
         <v>65000</v>
       </c>
-      <c r="F5" s="51">
+      <c r="F5" s="48">
         <v>65000</v>
       </c>
-      <c r="G5" s="50">
+      <c r="G5" s="66">
         <f>_xlfn.IFNA(_xlfn.XMATCH(F2, C:C, 0),"not found")</f>
         <v>2</v>
       </c>
@@ -4146,19 +4124,19 @@
       <c r="D6" s="48" t="s">
         <v>138</v>
       </c>
-      <c r="E6" s="50">
+      <c r="E6" s="66">
         <v>34000</v>
       </c>
-      <c r="F6" s="51">
+      <c r="F6" s="48">
         <v>45000</v>
       </c>
-      <c r="G6" s="50">
+      <c r="G6" s="66">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="gDgcE17w4/ORrqQPKTSRraJXqiNlrJ+Xo/Y3P3IMRFHiwWC770n0Gj4DyHv2FcRZT094OBb8dXayhnF2LPlvLA==" saltValue="8kYXIZhScHiHodzvNvTTRA==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="rBt43WfIP3BhYdBMrlE3UryPfB1FtQM3BN9qcF+eldvnlk4/VGEQTrXjuAdIadDPODYtfI1DcCzYwCrlVQgm1w==" saltValue="rBChixYQ1jOvcUuT5L9e+g==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -4177,158 +4155,159 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="22.9">
-      <c r="A1" s="60" t="s">
+      <c r="A1" s="57" t="s">
+        <v>158</v>
+      </c>
+      <c r="B1" s="57" t="s">
         <v>159</v>
       </c>
-      <c r="B1" s="60" t="s">
+      <c r="C1" s="57" t="s">
+        <v>161</v>
+      </c>
+      <c r="D1" s="57" t="s">
+        <v>162</v>
+      </c>
+      <c r="E1" s="57" t="s">
         <v>160</v>
       </c>
-      <c r="C1" s="60" t="s">
-        <v>162</v>
-      </c>
-      <c r="D1" s="60" t="s">
+      <c r="F1" s="57" t="s">
         <v>163</v>
       </c>
-      <c r="E1" s="60" t="s">
-        <v>161</v>
-      </c>
-      <c r="F1" s="60" t="s">
-        <v>164</v>
-      </c>
     </row>
     <row r="2" spans="1:6" ht="20.65">
-      <c r="A2" s="61" t="s">
+      <c r="A2" s="58" t="s">
         <v>83</v>
       </c>
-      <c r="B2" s="62">
+      <c r="B2" s="59">
         <v>39356</v>
       </c>
-      <c r="C2" s="62">
+      <c r="C2" s="59">
         <v>46027</v>
       </c>
-      <c r="D2" s="62">
+      <c r="D2" s="59">
         <v>46295</v>
       </c>
-      <c r="E2" s="61">
+      <c r="E2" s="58">
         <f>DATEDIF(B2,D2,"Y")</f>
         <v>18</v>
       </c>
-      <c r="F2" s="61">
+      <c r="F2" s="58">
         <f>D2-C2</f>
         <v>268</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="20.65">
-      <c r="A3" s="61" t="s">
+      <c r="A3" s="58" t="s">
         <v>118</v>
       </c>
-      <c r="B3" s="62">
+      <c r="B3" s="59">
         <v>39056</v>
       </c>
-      <c r="C3" s="62">
+      <c r="C3" s="59">
         <v>46065</v>
       </c>
-      <c r="D3" s="62">
+      <c r="D3" s="59">
         <v>46295</v>
       </c>
-      <c r="E3" s="61">
+      <c r="E3" s="58">
         <f t="shared" ref="E3:E7" si="0">DATEDIF(B3,D3,"Y")</f>
         <v>19</v>
       </c>
-      <c r="F3" s="61">
+      <c r="F3" s="58">
         <f t="shared" ref="F3:F7" si="1">D3-C3</f>
         <v>230</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="20.65">
-      <c r="A4" s="61" t="s">
+      <c r="A4" s="58" t="s">
         <v>85</v>
       </c>
-      <c r="B4" s="62">
+      <c r="B4" s="59">
         <v>29866</v>
       </c>
-      <c r="C4" s="62">
+      <c r="C4" s="59">
         <v>46205</v>
       </c>
-      <c r="D4" s="62">
+      <c r="D4" s="59">
         <v>46295</v>
       </c>
-      <c r="E4" s="61">
+      <c r="E4" s="58">
         <f t="shared" si="0"/>
         <v>44</v>
       </c>
-      <c r="F4" s="61">
+      <c r="F4" s="58">
         <f t="shared" si="1"/>
         <v>90</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="20.65">
-      <c r="A5" s="61" t="s">
+      <c r="A5" s="58" t="s">
         <v>84</v>
       </c>
-      <c r="B5" s="62">
+      <c r="B5" s="59">
         <v>31050</v>
       </c>
-      <c r="C5" s="62">
+      <c r="C5" s="59">
         <v>46026</v>
       </c>
-      <c r="D5" s="62">
+      <c r="D5" s="59">
         <v>46295</v>
       </c>
-      <c r="E5" s="61">
+      <c r="E5" s="58">
         <f t="shared" si="0"/>
         <v>41</v>
       </c>
-      <c r="F5" s="61">
+      <c r="F5" s="58">
         <f t="shared" si="1"/>
         <v>269</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="20.65">
-      <c r="A6" s="61" t="s">
+      <c r="A6" s="58" t="s">
         <v>89</v>
       </c>
-      <c r="B6" s="62">
+      <c r="B6" s="59">
         <v>20376</v>
       </c>
-      <c r="C6" s="62">
+      <c r="C6" s="59">
         <v>46029</v>
       </c>
-      <c r="D6" s="62">
+      <c r="D6" s="59">
         <v>46295</v>
       </c>
-      <c r="E6" s="61">
+      <c r="E6" s="58">
         <f t="shared" si="0"/>
         <v>70</v>
       </c>
-      <c r="F6" s="61">
+      <c r="F6" s="58">
         <f t="shared" si="1"/>
         <v>266</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="20.65">
-      <c r="A7" s="61" t="s">
+      <c r="A7" s="58" t="s">
         <v>86</v>
       </c>
-      <c r="B7" s="62">
+      <c r="B7" s="59">
         <v>41321</v>
       </c>
-      <c r="C7" s="62">
+      <c r="C7" s="59">
         <v>46239</v>
       </c>
-      <c r="D7" s="62">
+      <c r="D7" s="59">
         <v>46295</v>
       </c>
-      <c r="E7" s="61">
+      <c r="E7" s="58">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="F7" s="61">
+      <c r="F7" s="58">
         <f t="shared" si="1"/>
         <v>56</v>
       </c>
     </row>
   </sheetData>
+  <sheetProtection algorithmName="SHA-512" hashValue="CI7BfET+I9Mh9hQXNzU4hLX7l4Xoyr6vnbuo975iyOTFaUUprS3RzF8TLAuqqCTSD3Atp8oFjPdgBjezfMoWpA==" saltValue="hW91Zn06DTUbc6PGG5/oGA==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4347,90 +4326,91 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="23.25">
-      <c r="A1" s="52" t="s">
+      <c r="A1" s="49" t="s">
         <v>142</v>
       </c>
-      <c r="B1" s="52" t="s">
+      <c r="B1" s="49" t="s">
         <v>143</v>
       </c>
-      <c r="C1" s="55" t="s">
+      <c r="C1" s="52" t="s">
         <v>145</v>
       </c>
-      <c r="D1" s="56" t="s">
+      <c r="D1" s="53" t="s">
         <v>146</v>
       </c>
-      <c r="E1" s="56" t="s">
-        <v>148</v>
+      <c r="E1" s="53" t="s">
+        <v>147</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="23.25">
-      <c r="A2" s="53" t="s">
+      <c r="A2" s="50" t="s">
         <v>33</v>
       </c>
-      <c r="B2" s="53">
+      <c r="B2" s="50">
         <v>50000</v>
       </c>
-      <c r="C2" s="55">
+      <c r="C2" s="52">
         <f ca="1">SUM(INDIRECT("B2:B6"))</f>
         <v>200000</v>
       </c>
-      <c r="D2" s="56" t="s">
-        <v>147</v>
-      </c>
-      <c r="E2" s="56" cm="1">
+      <c r="D2" s="53" t="s">
+        <v>173</v>
+      </c>
+      <c r="E2" s="53" cm="1">
         <f t="array" aca="1" ref="E2" ca="1">INDIRECT(D2)</f>
+        <v>40000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="22.15">
+      <c r="A3" s="50" t="s">
+        <v>34</v>
+      </c>
+      <c r="B3" s="50">
         <v>30000</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" ht="22.15">
-      <c r="A3" s="53" t="s">
-        <v>34</v>
-      </c>
-      <c r="B3" s="53">
-        <v>30000</v>
-      </c>
-      <c r="C3" s="54">
+      <c r="C3" s="51">
         <f ca="1">SUM(INDIRECT("B2:B6"))</f>
         <v>200000</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="22.15">
-      <c r="A4" s="53" t="s">
+      <c r="A4" s="50" t="s">
         <v>35</v>
       </c>
-      <c r="B4" s="53">
+      <c r="B4" s="50">
         <v>40000</v>
       </c>
-      <c r="C4" s="54">
-        <f t="shared" ref="C3:C6" ca="1" si="0">SUM(INDIRECT("B2:B6"))</f>
+      <c r="C4" s="51">
+        <f t="shared" ref="C4:C6" ca="1" si="0">SUM(INDIRECT("B2:B6"))</f>
         <v>200000</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="22.15">
-      <c r="A5" s="53" t="s">
+      <c r="A5" s="50" t="s">
         <v>144</v>
       </c>
-      <c r="B5" s="53">
+      <c r="B5" s="50">
         <v>60000</v>
       </c>
-      <c r="C5" s="54">
+      <c r="C5" s="51">
         <f ca="1">SUM(INDIRECT("B2:B6"))</f>
         <v>200000</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="22.15">
-      <c r="A6" s="53" t="s">
+      <c r="A6" s="50" t="s">
         <v>36</v>
       </c>
-      <c r="B6" s="53">
+      <c r="B6" s="50">
         <v>20000</v>
       </c>
-      <c r="C6" s="54">
+      <c r="C6" s="51">
         <f t="shared" ca="1" si="0"/>
         <v>200000</v>
       </c>
     </row>
   </sheetData>
+  <sheetProtection algorithmName="SHA-512" hashValue="KuVu5IhnLABEsFCvUBasn7WAl17yQgbdGUWNgNNvm6VXlxzmHIgkihOGXvHo7DcyUaNLlmPvtH3p1mAYLDY0Uw==" saltValue="whyv62DSdDD5uMrxU4lC0w==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -4447,144 +4427,145 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="17.25">
-      <c r="A1" s="66" t="s">
+      <c r="A1" s="63" t="s">
         <v>113</v>
       </c>
-      <c r="B1" s="66" t="s">
+      <c r="B1" s="63" t="s">
         <v>131</v>
       </c>
-      <c r="C1" s="66" t="s">
+      <c r="C1" s="63" t="s">
         <v>124</v>
       </c>
-      <c r="D1" s="66" t="s">
+      <c r="D1" s="63" t="s">
+        <v>165</v>
+      </c>
+      <c r="E1" s="63" t="s">
         <v>166</v>
       </c>
-      <c r="E1" s="66" t="s">
+      <c r="F1" s="63" t="s">
         <v>167</v>
       </c>
-      <c r="F1" s="66" t="s">
-        <v>168</v>
-      </c>
     </row>
     <row r="2" spans="1:6" ht="17.25">
-      <c r="A2" s="64">
+      <c r="A2" s="61">
         <v>1</v>
       </c>
-      <c r="B2" s="64" t="s">
+      <c r="B2" s="61" t="s">
         <v>119</v>
       </c>
-      <c r="C2" s="64">
+      <c r="C2" s="61">
         <v>233.58</v>
       </c>
-      <c r="D2" s="64">
+      <c r="D2" s="61">
         <f>ROUND(C2,-2)</f>
         <v>200</v>
       </c>
-      <c r="E2" s="64">
+      <c r="E2" s="61">
         <f>CEILING(C2,100)</f>
         <v>300</v>
       </c>
-      <c r="F2" s="64">
+      <c r="F2" s="61">
         <f>FLOOR(C2,100)</f>
         <v>200</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="17.25">
-      <c r="A3" s="64">
+      <c r="A3" s="61">
         <v>2</v>
       </c>
-      <c r="B3" s="64" t="s">
+      <c r="B3" s="61" t="s">
         <v>123</v>
       </c>
-      <c r="C3" s="64">
+      <c r="C3" s="61">
         <v>456.7</v>
       </c>
-      <c r="D3" s="64">
+      <c r="D3" s="61">
         <f t="shared" ref="D3:D6" si="0">ROUND(C3,-2)</f>
         <v>500</v>
       </c>
-      <c r="E3" s="64">
+      <c r="E3" s="61">
         <f t="shared" ref="E3:E6" si="1">CEILING(C3,100)</f>
         <v>500</v>
       </c>
-      <c r="F3" s="64">
+      <c r="F3" s="61">
         <f t="shared" ref="F3:F6" si="2">FLOOR(C3,100)</f>
         <v>400</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="17.25">
-      <c r="A4" s="64">
+      <c r="A4" s="61">
         <v>3</v>
       </c>
-      <c r="B4" s="64" t="s">
-        <v>169</v>
-      </c>
-      <c r="C4" s="64">
+      <c r="B4" s="61" t="s">
+        <v>168</v>
+      </c>
+      <c r="C4" s="61">
         <v>5437.8</v>
       </c>
-      <c r="D4" s="64">
+      <c r="D4" s="61">
         <f t="shared" si="0"/>
         <v>5400</v>
       </c>
-      <c r="E4" s="64">
+      <c r="E4" s="61">
         <f t="shared" si="1"/>
         <v>5500</v>
       </c>
-      <c r="F4" s="64">
+      <c r="F4" s="61">
         <f t="shared" si="2"/>
         <v>5400</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="17.25">
-      <c r="A5" s="64">
+      <c r="A5" s="61">
         <v>4</v>
       </c>
-      <c r="B5" s="64" t="s">
-        <v>165</v>
-      </c>
-      <c r="C5" s="64">
+      <c r="B5" s="61" t="s">
+        <v>164</v>
+      </c>
+      <c r="C5" s="61">
         <v>43245.875999999997</v>
       </c>
-      <c r="D5" s="64">
+      <c r="D5" s="61">
         <f t="shared" si="0"/>
         <v>43200</v>
       </c>
-      <c r="E5" s="64">
+      <c r="E5" s="61">
         <f t="shared" si="1"/>
         <v>43300</v>
       </c>
-      <c r="F5" s="64">
+      <c r="F5" s="61">
         <f t="shared" si="2"/>
         <v>43200</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="17.649999999999999" thickBot="1">
-      <c r="A6" s="65">
+      <c r="A6" s="62">
         <v>5</v>
       </c>
-      <c r="B6" s="65" t="s">
+      <c r="B6" s="62" t="s">
         <v>133</v>
       </c>
-      <c r="C6" s="65">
+      <c r="C6" s="62">
         <v>54356.87</v>
       </c>
-      <c r="D6" s="65">
+      <c r="D6" s="62">
         <f t="shared" si="0"/>
         <v>54400</v>
       </c>
-      <c r="E6" s="65">
+      <c r="E6" s="62">
         <f t="shared" si="1"/>
         <v>54400</v>
       </c>
-      <c r="F6" s="65">
+      <c r="F6" s="62">
         <f t="shared" si="2"/>
         <v>54300</v>
       </c>
     </row>
     <row r="20" spans="11:11" ht="16.5">
-      <c r="K20" s="63"/>
+      <c r="K20" s="60"/>
     </row>
   </sheetData>
+  <sheetProtection algorithmName="SHA-512" hashValue="Vrh+ZAVV2T8W1L96yG1nkkNvTGAG/AsTO5ZWn1VV43Y966gkxK2AnJsOySWwBybXEoC8GwnIm+Cnq7nvFVBYDQ==" saltValue="L5GYvhRv59pc1zJtjoaxDg==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -4601,99 +4582,100 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="20.25">
-      <c r="A1" s="67" t="s">
+      <c r="A1" s="64" t="s">
+        <v>169</v>
+      </c>
+      <c r="B1" s="64" t="s">
+        <v>158</v>
+      </c>
+      <c r="C1" s="64" t="s">
         <v>170</v>
       </c>
-      <c r="B1" s="67" t="s">
-        <v>159</v>
-      </c>
-      <c r="C1" s="67" t="s">
+      <c r="D1" s="64" t="s">
         <v>171</v>
       </c>
-      <c r="D1" s="67" t="s">
-        <v>172</v>
-      </c>
-      <c r="E1" s="67"/>
+      <c r="E1" s="64"/>
     </row>
     <row r="2" spans="1:5" ht="20.25">
-      <c r="A2" s="68">
+      <c r="A2" s="65">
         <v>201</v>
       </c>
-      <c r="B2" s="68" t="s">
+      <c r="B2" s="65" t="s">
         <v>83</v>
       </c>
-      <c r="C2" s="68">
+      <c r="C2" s="65">
         <v>78</v>
       </c>
-      <c r="D2" s="68" t="str" cm="1">
+      <c r="D2" s="65" t="str" cm="1">
         <f t="array" ref="D2:E4">_xlfn._xlws.FILTER(B2:C6,C2:C6&gt;=75)</f>
         <v>VAIDEHI</v>
       </c>
-      <c r="E2" s="68">
+      <c r="E2" s="65">
         <v>78</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="20.25">
-      <c r="A3" s="68">
+      <c r="A3" s="65">
         <v>202</v>
       </c>
-      <c r="B3" s="68" t="s">
+      <c r="B3" s="65" t="s">
         <v>118</v>
       </c>
-      <c r="C3" s="68">
+      <c r="C3" s="65">
         <v>76</v>
       </c>
-      <c r="D3" s="68" t="str">
+      <c r="D3" s="65" t="str">
         <v>VEDANT</v>
       </c>
-      <c r="E3" s="68">
+      <c r="E3" s="65">
         <v>76</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="20.25">
-      <c r="A4" s="68">
+      <c r="A4" s="65">
         <v>203</v>
       </c>
-      <c r="B4" s="68" t="s">
+      <c r="B4" s="65" t="s">
         <v>84</v>
       </c>
-      <c r="C4" s="68">
+      <c r="C4" s="65">
         <v>75</v>
       </c>
-      <c r="D4" s="68" t="str">
+      <c r="D4" s="65" t="str">
         <v>MEGHA</v>
       </c>
-      <c r="E4" s="68">
+      <c r="E4" s="65">
         <v>75</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="20.25">
-      <c r="A5" s="68">
+      <c r="A5" s="65">
         <v>204</v>
       </c>
-      <c r="B5" s="68" t="s">
+      <c r="B5" s="65" t="s">
         <v>85</v>
       </c>
-      <c r="C5" s="68">
+      <c r="C5" s="65">
         <v>74</v>
       </c>
-      <c r="D5" s="68"/>
-      <c r="E5" s="68"/>
+      <c r="D5" s="65"/>
+      <c r="E5" s="65"/>
     </row>
     <row r="6" spans="1:5" ht="20.25">
-      <c r="A6" s="68">
+      <c r="A6" s="65">
         <v>205</v>
       </c>
-      <c r="B6" s="68" t="s">
+      <c r="B6" s="65" t="s">
         <v>86</v>
       </c>
-      <c r="C6" s="68">
+      <c r="C6" s="65">
         <v>73</v>
       </c>
-      <c r="D6" s="68"/>
-      <c r="E6" s="68"/>
+      <c r="D6" s="65"/>
+      <c r="E6" s="65"/>
     </row>
   </sheetData>
+  <sheetProtection algorithmName="SHA-512" hashValue="tXDJxRNHQB2TLLFPsEz4qtxY6CDvZ5vqK0QrTVPu4w89BVvmbgUkVZxeLmn+WQX+cR6GKMO1smpbp5S0jWhrHA==" saltValue="GTPhYyLghNYecvbaQL6mMQ==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -4709,117 +4691,117 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="19.899999999999999">
-      <c r="A1" s="58" t="s">
+      <c r="A1" s="55" t="s">
+        <v>148</v>
+      </c>
+      <c r="B1" s="55" t="s">
+        <v>152</v>
+      </c>
+      <c r="C1" s="55" t="s">
+        <v>153</v>
+      </c>
+      <c r="D1" s="55" t="s">
         <v>149</v>
       </c>
-      <c r="B1" s="58" t="s">
-        <v>153</v>
-      </c>
-      <c r="C1" s="58" t="s">
+      <c r="E1" s="55" t="s">
         <v>154</v>
       </c>
-      <c r="D1" s="58" t="s">
+      <c r="F1" s="55" t="s">
         <v>150</v>
       </c>
-      <c r="E1" s="58" t="s">
+      <c r="G1" s="55" t="s">
         <v>155</v>
       </c>
-      <c r="F1" s="58" t="s">
-        <v>151</v>
-      </c>
-      <c r="G1" s="58" t="s">
+      <c r="H1" s="55" t="s">
         <v>156</v>
       </c>
-      <c r="H1" s="58" t="s">
+    </row>
+    <row r="2" spans="1:8" ht="19.899999999999999">
+      <c r="A2" s="55" t="s">
         <v>157</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" ht="19.899999999999999">
-      <c r="A2" s="58" t="s">
-        <v>158</v>
-      </c>
-      <c r="B2" s="58">
+      <c r="B2" s="55">
         <v>11000</v>
       </c>
-      <c r="C2" s="58">
+      <c r="C2" s="55">
         <v>23000</v>
       </c>
-      <c r="D2" s="58">
+      <c r="D2" s="55">
         <v>34000</v>
       </c>
-      <c r="E2" s="58">
+      <c r="E2" s="55">
         <v>78000</v>
       </c>
-      <c r="F2" s="58">
+      <c r="F2" s="55">
         <v>67000</v>
       </c>
-      <c r="G2" s="58">
+      <c r="G2" s="55">
         <v>65000</v>
       </c>
-      <c r="H2" s="58">
+      <c r="H2" s="55">
         <v>56700</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="19.899999999999999">
-      <c r="A3" s="57"/>
-      <c r="B3" s="57"/>
-      <c r="C3" s="57"/>
-      <c r="D3" s="57"/>
-      <c r="E3" s="57"/>
-      <c r="F3" s="57"/>
-      <c r="G3" s="57"/>
-      <c r="H3" s="57"/>
+      <c r="A3" s="54"/>
+      <c r="B3" s="54"/>
+      <c r="C3" s="54"/>
+      <c r="D3" s="54"/>
+      <c r="E3" s="54"/>
+      <c r="F3" s="54"/>
+      <c r="G3" s="54"/>
+      <c r="H3" s="54"/>
     </row>
     <row r="4" spans="1:8" ht="19.899999999999999">
-      <c r="A4" s="57"/>
-      <c r="B4" s="57"/>
-      <c r="C4" s="57"/>
-      <c r="D4" s="57"/>
-      <c r="E4" s="57"/>
-      <c r="F4" s="57"/>
-      <c r="G4" s="57"/>
-      <c r="H4" s="57"/>
+      <c r="A4" s="54"/>
+      <c r="B4" s="54"/>
+      <c r="C4" s="54"/>
+      <c r="D4" s="54"/>
+      <c r="E4" s="54"/>
+      <c r="F4" s="54"/>
+      <c r="G4" s="54"/>
+      <c r="H4" s="54"/>
     </row>
     <row r="5" spans="1:8" ht="19.899999999999999">
-      <c r="A5" s="59" t="s">
-        <v>149</v>
-      </c>
-      <c r="B5" s="59">
+      <c r="A5" s="56" t="s">
+        <v>148</v>
+      </c>
+      <c r="B5" s="56">
         <v>4</v>
       </c>
-      <c r="C5" s="59"/>
-      <c r="D5" s="59" cm="1">
+      <c r="C5" s="56"/>
+      <c r="D5" s="56" cm="1">
         <f t="array" aca="1" ref="D5:G5" ca="1">OFFSET(B2,0,0,1,B5)</f>
         <v>11000</v>
       </c>
-      <c r="E5" s="59">
+      <c r="E5" s="56">
         <f ca="1"/>
         <v>23000</v>
       </c>
-      <c r="F5" s="59">
+      <c r="F5" s="56">
         <f ca="1"/>
         <v>34000</v>
       </c>
-      <c r="G5" s="59">
+      <c r="G5" s="56">
         <f ca="1"/>
         <v>78000</v>
       </c>
-      <c r="H5" s="59"/>
+      <c r="H5" s="56"/>
     </row>
     <row r="6" spans="1:8" ht="19.899999999999999">
-      <c r="A6" s="59" t="s">
-        <v>152</v>
-      </c>
-      <c r="B6" s="59">
+      <c r="A6" s="56" t="s">
+        <v>151</v>
+      </c>
+      <c r="B6" s="56">
         <f ca="1">SUM(OFFSET($B$2,0,0,1,$B$5))</f>
         <v>146000</v>
       </c>
-      <c r="C6" s="59"/>
-      <c r="D6" s="59"/>
-      <c r="E6" s="59"/>
-      <c r="F6" s="59"/>
-      <c r="G6" s="59"/>
-      <c r="H6" s="59"/>
+      <c r="C6" s="56"/>
+      <c r="D6" s="56"/>
+      <c r="E6" s="56"/>
+      <c r="F6" s="56"/>
+      <c r="G6" s="56"/>
+      <c r="H6" s="56"/>
     </row>
     <row r="19" spans="18:18">
       <c r="R19">
@@ -4827,6 +4809,7 @@
       </c>
     </row>
   </sheetData>
+  <sheetProtection algorithmName="SHA-512" hashValue="UzxQ3HT8J3SXuPfIM7LtnIJ5fLrdOspMCwYfV36BWvNxMG0m9m1boDBIENr0RYBQ6Y7aolUrt7NgWkwHUmaloQ==" saltValue="tgdBtoyjh/YILZfDaFYKhg==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5324,6 +5307,7 @@
       <c r="B24" s="20"/>
     </row>
   </sheetData>
+  <sheetProtection algorithmName="SHA-512" hashValue="WK1HHpxzTiCzWyZjtsTFnx92lzMFJ6Nqvzyza93r01d+ri77mJep3dXu0iBOuoypi7r7KPEplYfRBPfQdbOLzw==" saltValue="P/1l59HQLirUaQ5LtDU4rg==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
